--- a/output/topology_excel/8714.xlsx
+++ b/output/topology_excel/8714.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,57 +490,75 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>510914</v>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2744</v>
+        <v>42120</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>94</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>110599</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>426</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5964</v>
+        <v>510914</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -533,110 +566,146 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>114755</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1095</v>
+        <v>510914</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>86</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>311</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5532</v>
+        <v>25146</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>68</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>23389</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1204</v>
+        <v>25146</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>56</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>95</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1330</v>
+        <v>15238</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>62</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -649,81 +718,108 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>952</v>
+        <v>14938</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>62</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>708</v>
+        <v>121724</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>82</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>154</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2750</v>
+        <v>88692</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -736,197 +832,260 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>868</v>
+        <v>42120</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>102</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>110599</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>239</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3231</v>
+        <v>114755</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>412</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>110599</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>868</v>
+        <v>510914</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>451</v>
+      </c>
+      <c r="J13" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>110599</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>255</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3570</v>
+        <v>15238</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>125</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>110599</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1230</v>
+        <v>14938</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>134</v>
+      </c>
+      <c r="J15" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>114755</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>121</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3003</v>
+        <v>23389</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>205</v>
+      </c>
+      <c r="J16" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>114755</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1185</v>
+        <v>510914</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -939,168 +1098,222 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>342</v>
-      </c>
-      <c r="G18" t="n">
-        <v>9436</v>
+        <v>15238</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>139</v>
+      </c>
+      <c r="J18" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>412</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5768</v>
+        <v>14938</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>148</v>
+      </c>
+      <c r="J19" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>125</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1750</v>
+        <v>23389</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>103</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>134</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3152</v>
+        <v>25146</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>224</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" t="n">
-        <v>7348</v>
+        <v>88692</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>488</v>
+      </c>
+      <c r="J22" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>191</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2674</v>
+        <v>121724</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>121</v>
+      </c>
+      <c r="J23" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1326,32 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>510914</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5684</v>
+        <v>42120</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>284</v>
+      </c>
+      <c r="J24" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="25">
@@ -1142,110 +1364,222 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>23389</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>53</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6413</v>
+        <v>25146</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>137</v>
+      </c>
+      <c r="J25" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>23389</v>
+      </c>
+      <c r="D26" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>127</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1905</v>
+        <v>121724</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>121</v>
+      </c>
+      <c r="J26" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>15238</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>324</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4860</v>
+        <v>14938</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>121</v>
+      </c>
+      <c r="J27" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25146</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>121724</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>127</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>8</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>88692</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>121724</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>368</v>
+      </c>
+      <c r="J29" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>88692</v>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
+        <v>42120</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>270</v>
       </c>
-      <c r="G28" t="n">
-        <v>4050</v>
+      <c r="J30" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8714.xlsx
+++ b/output/topology_excel/8714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,26 +482,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>510914</v>
+        <v>110599</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42120</v>
+        <v>510914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,15 +512,15 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>110599</v>
+        <v>114755</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -543,52 +543,52 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114755</v>
+        <v>510914</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>510914</v>
+        <v>25146</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
@@ -596,15 +596,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>510914</v>
+        <v>23389</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -619,33 +619,33 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23389</v>
+        <v>510914</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -653,21 +653,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>25146</v>
+        <v>15238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J6" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -683,19 +683,19 @@
         <v>510914</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15238</v>
+        <v>14938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -721,29 +721,29 @@
         <v>510914</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>14938</v>
+        <v>121724</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -759,7 +759,7 @@
         <v>510914</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -767,18 +767,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>121724</v>
+        <v>88692</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J9" t="n">
         <v>15</v>
@@ -797,29 +797,29 @@
         <v>510914</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>88692</v>
+        <v>42120</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="J11" t="n">
         <v>14</v>
@@ -930,10 +930,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>451</v>
+        <v>302</v>
       </c>
       <c r="J13" t="n">
-        <v>149</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1196,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -1272,10 +1272,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>488</v>
+        <v>259</v>
       </c>
       <c r="J22" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
@@ -1394,26 +1394,26 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15238</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>23389</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>121724</v>
+        <v>14938</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1427,12 +1427,12 @@
         <v>121</v>
       </c>
       <c r="J26" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1440,18 +1440,18 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15238</v>
+        <v>25146</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14938</v>
+        <v>121724</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,23 +1462,23 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J27" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25146</v>
+        <v>88692</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1500,10 +1500,10 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>127</v>
+        <v>368</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
@@ -1519,15 +1519,15 @@
         <v>88692</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>121724</v>
+        <v>42120</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,47 +1538,9 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="J29" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>88692</v>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>42120</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>270</v>
-      </c>
-      <c r="J30" t="n">
         <v>15</v>
       </c>
     </row>

--- a/output/topology_excel/8714.xlsx
+++ b/output/topology_excel/8714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>412</v>
+        <v>363</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>302</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,15 +762,15 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>205</v>
+        <v>412</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="F19" t="n">
-        <v>135</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,15 +916,15 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>259</v>
+        <v>368</v>
       </c>
       <c r="F22" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>9</v>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>170</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F25" t="n">
-        <v>130</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="F28" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
@@ -1059,21 +1059,153 @@
         <v>8</v>
       </c>
       <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>224</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>156</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>10</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>270</v>
-      </c>
-      <c r="F29" t="n">
-        <v>15</v>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>98</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>148</v>
+      </c>
+      <c r="F32" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>159</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>228</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>140</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8714.xlsx
+++ b/output/topology_excel/8714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
         </is>
       </c>
     </row>
@@ -481,6 +521,14 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +551,14 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +581,14 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +611,14 @@
       <c r="F5" t="n">
         <v>34</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +641,14 @@
       <c r="F6" t="n">
         <v>14</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +671,14 @@
       <c r="F7" t="n">
         <v>14</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +701,14 @@
       <c r="F8" t="n">
         <v>15</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +731,14 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +761,14 @@
       <c r="F10" t="n">
         <v>14</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +791,14 @@
       <c r="F11" t="n">
         <v>14</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -693,14 +813,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>363</v>
+        <v>164</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +855,14 @@
       <c r="F13" t="n">
         <v>14</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,14 +877,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>302</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>202</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -759,14 +911,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>101</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +953,14 @@
       <c r="F16" t="n">
         <v>14</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +983,14 @@
       <c r="F17" t="n">
         <v>14</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -831,8 +1011,16 @@
         <v>134</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,14 +1035,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1077,14 @@
       <c r="F20" t="n">
         <v>14</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -891,14 +1099,26 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="F21" t="n">
-        <v>99</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>84</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -919,8 +1139,16 @@
         <v>368</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1171,14 @@
       <c r="F23" t="n">
         <v>15</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -963,8 +1199,16 @@
         <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>59</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1231,14 @@
       <c r="F25" t="n">
         <v>15</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1007,8 +1259,16 @@
         <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>69</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,14 +1283,26 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>126</v>
+      </c>
+      <c r="H27" t="n">
+        <v>14</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1045,13 +1317,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F28" t="n">
-        <v>130</v>
+        <v>19</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>14</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1075,6 +1371,14 @@
       <c r="F29" t="n">
         <v>14</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1401,14 @@
       <c r="F30" t="n">
         <v>14</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1117,8 +1429,16 @@
         <v>98</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1133,14 +1453,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>134</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1155,7 +1487,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>159</v>
@@ -1163,14 +1495,26 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
+      <c r="G33" t="n">
+        <v>228</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
         <v>2</v>
       </c>
-      <c r="B34" t="n">
-        <v>12</v>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>Opening</t>
@@ -1180,33 +1524,19 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>140</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
